--- a/important_mails_2026-07-10.xlsx
+++ b/important_mails_2026-07-10.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H293"/>
+  <dimension ref="A1:H283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7709,7 +7709,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>KYC审核类</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -7724,178 +7724,21 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Wed, 10 Jun 2026 04:19:55 +0000</t>
+          <t>Thu, 18 Jun 2026 14:32:29 +0000</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (wrlLFrQcT3)</t>
+          <t>Seller News: June 2026</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-4911916-4537164
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-1460153102261163</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 9 Jun 2026 18:59:47 +0000</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (2605311NRC)</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-1914736-1200225
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-686096915804077</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 9 Jun 2026 16:46:32 +0000</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID Fqz6Dy+EsU
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on June 10, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-1196270873423063</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>KYC审核类</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 18 Jun 2026 14:32:29 +0000</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>Seller News: June 2026</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7912,39 +7755,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 14:39:15 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7961,39 +7804,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 10:10:03 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -8017,39 +7860,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 17:09:13 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Access your January–March 2026 China tax report</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -8065,39 +7908,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 16:54:53 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Access your January - March 2026 China tax report</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -8113,39 +7956,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8165,39 +8008,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:43:29 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8214,39 +8057,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:42:06 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8266,39 +8109,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:21:30 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8318,39 +8161,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8367,39 +8210,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 03:31:27 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8419,39 +8262,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 03:28:55 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8471,39 +8314,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:38:10 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8520,39 +8363,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:37:54 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8572,39 +8415,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:52:57 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8621,39 +8464,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:51:45 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8673,39 +8516,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:45:52 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8725,39 +8568,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 01:48:12 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Updated China tax report link for October - December 2025</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
  We’re resending your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -8775,39 +8618,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 16:59:05 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -8823,39 +8666,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 14:09:38 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8875,39 +8718,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 14:09:19 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8924,39 +8767,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 16:37:09 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;informacion-vendedor@amazon.mx&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Pago del saldo en tu cuenta de pagos de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>Estimado vendedor:
  Hemos realizado un cargo en tu tarjeta de crédito (Visa) por valor de MXN 192.85 con el fin de saldar tu cuenta de vendedor de Amazon.
@@ -8968,39 +8811,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 14:05:42 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9020,39 +8863,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 12:44:57 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9069,39 +8912,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Sun, 21 Jun 2026 12:50:33 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9121,39 +8964,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 13:23:55 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9170,39 +9013,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 13:11:15 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9222,39 +9065,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 13:09:47 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9271,39 +9114,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 17:21:56 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January–March 2026</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -9320,39 +9163,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 16:54:51 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -9369,39 +9212,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 08:40:50 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Envía el número de registro de España para la responsabilidad ampliada del productor con respecto a los RAEE a más tardar el 30 de septiembre</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Presenta el número de registro de la responsabilidad ampliada del productor a más tardar el 30 de septiembre o se te inscribirá automáticamente en RAP: Pago en mi nombre.
  96
@@ -9410,39 +9253,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 14:39:03 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9462,39 +9305,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:27:04 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9514,39 +9357,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:25:49 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9563,39 +9406,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:24:48 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9615,39 +9458,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 06:40:46 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Seller Central &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>重要信息：即刻重新验证您的所有 付款账户或存款方式</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>96
  亲爱的卖家，
@@ -9681,39 +9524,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 14:24:03 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9733,39 +9576,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 14:23:28 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9782,39 +9625,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 13:35:44 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9834,39 +9677,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:28:40 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9886,39 +9729,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:24:36 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9935,39 +9778,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:24:04 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9987,39 +9830,39 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 23:31:42 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10039,39 +9882,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 12:54:19 +0000</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10091,39 +9934,39 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 15:13:12 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 42.71. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -10137,39 +9980,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 11:53:43 +0000</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10189,39 +10032,39 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 11:51:09 +0000</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10238,39 +10081,39 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 16:29:28 +0000</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;informacion-vendedor@amazon.mx&gt;</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Pago del saldo en tu cuenta de pagos de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>Estimado vendedor:
  Hemos realizado un cargo en tu tarjeta de crédito (Visa) por valor de MXN 90.75 con el fin de saldar tu cuenta de vendedor de Amazon.
@@ -10282,193 +10125,40 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 02:57:49 +0000</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F190" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement attempted
-Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
-On 06/10/26 02:57 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
- 734.55.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon Store,
-Amazon Services
-Help us improve your payment experience on Amaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 02:56:47 +0000</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F191" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 06/10/26 02:56 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 480,87.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 02:56:35 +0000</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 06/10/26 02:56 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
- 239.53.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 06:41:28 +0000</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -10483,39 +10173,39 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:09:44 +0000</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant is now live in France, Italy &amp; Spain</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  AI-powered assistance is now available in Seller Central to help you manage your business more efficiently.
@@ -10533,40 +10223,40 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 13:15:52 +0000</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>The Amazon Accelerate 2026 speaker lineup is here! Register now to
  save $100</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z49sbm/6744236849/h/wes7VJdAGIYNS4DfvXPWWwdvIH7_mIadF_Oxp_jSZW8)
 [Speakers at Accelerate](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z49sbq/6744236849/h/wes7VJdAGIYNS4DfvXPWWwdvIH7_mIadF_Oxp_jSZW8)
@@ -10583,40 +10273,40 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 04:09:19 +0000</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -10628,40 +10318,40 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 04:08:32 +0000</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -10673,40 +10363,40 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 02:52:15 +0000</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -10725,39 +10415,39 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 12:40:58 +0000</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -10773,39 +10463,39 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:56:40 +0000</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -10831,39 +10521,39 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:39:22 +0000</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -10889,39 +10579,39 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 10:15:17 +0000</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>Submit EPR registration numbers by June 30</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -10930,39 +10620,39 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 04:34:37 +0000</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -10987,40 +10677,40 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 06:03:25 +0000</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -11038,40 +10728,40 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 19:23:07 +0000</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -11096,39 +10786,39 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:11:59 +0000</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -11147,39 +10837,39 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:09:32 +0000</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -11198,39 +10888,39 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:09:28 +0000</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -11249,39 +10939,39 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:32:14 +0000</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>"pars-rp-core-sellerappeals-transfer@amazon.com" &lt;pars-rp-core-sellerappeals-transfer@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20516062511] 危险物品（危险品）</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20516062511] 危险物品（危险品）
@@ -11309,39 +10999,39 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:13:22 +0000</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -11360,39 +11050,39 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 20:37:03 +0000</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Important message: your account is at risk of deactivation</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>96
  96
@@ -11412,40 +11102,40 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 06:46:26 +0000</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -11461,40 +11151,40 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 10:18:49 +0000</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -11521,39 +11211,39 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 03:03:53 +0000</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>Review issue on FBA Shipment (FBA1234567)</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>96
  Review shipment defects to avoid reoccurrence
@@ -11573,40 +11263,40 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 13:54:53 +0000</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -11619,40 +11309,40 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 10:51:40 +0000</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -11671,39 +11361,39 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 13:08:16 +0000</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -11722,40 +11412,40 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 04:06:26 +0000</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.ca" &lt;cscompliance-docreview-vendor@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC - DOC REVIEW
@@ -11771,39 +11461,39 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 19:04:36 +0000</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>New EU restriction on textile and footwear disposal</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>96
  By July 19, update your removal settings for apparel, clothing and footwear in EU fulfillment centers
@@ -11818,39 +11508,39 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 18:11:21 +0000</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -11868,134 +11558,39 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 02:29:01 +0000</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr">
-        <is>
-          <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F221" s="2" t="inlineStr">
-        <is>
-          <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
- MARKETPLACE: 1 - PS - APPEAL</t>
-        </is>
-      </c>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
-Hello,
-We received your appeal. We recognize compliance may be confusing or frustrating. However, as before, the product has characteristics of Arts &amp; Crafts for children. Fulfilling compliance obligations is required for selling your products on our store. As a next step, you must take the following action:
-To ensure that your product is not removed from Amazon's US store, you require a test result that confirms your product's compliance with Amazon's Policy. Please initiate a test request for each product to one of the third-party Testing, Inspection, and Certification organizations through Account Health dashboard. See our third-party TIC services help page to learn more: https://sellercentral.amazon.com/help/hub/reference/external/GUTZ2R2DD6P2UMVB . If you are still unclear and have questions, please include comments when submitting your appeal so that we can provide help.
-For more information on compliance requirements for Arts &amp; Crafts, please visit: https://sellercentral.amazon.com/help/hub/reference/external/GKJRA3FRPRKVBJJS
-Once testing or verification is requested, please work </t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 9 Jun 2026 18:10:54 +0000</t>
-        </is>
-      </c>
-      <c r="E222" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F222" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:26:45 +0000</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>El Asistente de vendedores ya está activo en Francia, Italia y España</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>96
  La asistencia con tecnología de IA ya está disponible en Seller Central para ayudarte a gestionar tu negocio de forma más eficiente.
@@ -12009,39 +11604,39 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:11:01 +0000</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -12059,39 +11654,39 @@
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 13:49:18 +0000</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>L'assistente venditori è ora attivo in Francia, Italia e Spagna</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  L'assistenza basata su AI è ora disponibile in Seller Central per aiutarti a gestire la tua attività in modo più efficiente.
@@ -12106,39 +11701,39 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 16:04:35 +0000</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Presentar información de cumplimiento normativo de la RAP en Portugal</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>96
  La normativa portuguesa sobre la RAP se aplica a los productos vendidos a clientes de Portugal.
@@ -12155,39 +11750,39 @@
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 02:53:05 +0000</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 06/2026</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -12205,39 +11800,39 @@
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 00:26:34 +0000</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12929127032&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12929127032&lt;/p&gt;
@@ -12252,39 +11847,39 @@
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:10:24 +0000</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -12300,39 +11895,39 @@
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:40:10 +0000</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -12347,39 +11942,39 @@
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:07:09 +0000</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -12407,39 +12002,39 @@
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 22:31:41 +0000</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para julio</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para julio
@@ -12468,39 +12063,39 @@
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 01:48:42 +0000</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Łącze do zaktualizowanego raportu podatkowego dotyczącego Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>96
  Ponownie przesyłamy kwartalny raport podatkowy, który obejmuje dane takie jak informacje o tożsamości, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -12518,39 +12113,39 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 10:01:00 +0000</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -12569,39 +12164,39 @@
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 16:59:26 +0000</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -12615,39 +12210,39 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 00:26:49 +0000</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;
@@ -12662,39 +12257,39 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 09:29:52 +0000</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>Prime会员日明天开始：最后提报促销活动的机会</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -12718,39 +12313,39 @@
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>Sun, 21 Jun 2026 12:49:43 +0000</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -12765,39 +12360,39 @@
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 10:18:43 +0000</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -12818,39 +12413,39 @@
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 10:02:13 +0000</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>最后机会：请于6月19日前提报 Prime Day 促销</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -12873,39 +12468,39 @@
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 14:18:31 +0000</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -12925,39 +12520,39 @@
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 10:14:39 +0000</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>Soumettre les numéros d'enregistrement REP avant le 30 juin</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -12966,39 +12561,39 @@
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 09:11:12 +0000</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>Seller News: June 2026</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr"/>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -13018,40 +12613,40 @@
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 17:13:19 +0000</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>Get increased New Selection Program (2026) benefits starting July
  30</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>96
  Effective July 30, 2026, the New Selection Program (2026) launches with increased benefits to help you launch new branded products with reduced costs and complexity while boosting early sales.
@@ -13065,39 +12660,39 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 00:29:05 +0000</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12891299002&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12891299002&lt;/p&gt;
@@ -13113,39 +12708,39 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:26:46 +0000</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -13160,39 +12755,39 @@
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:13:30 +0000</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -13209,39 +12804,39 @@
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:12:43 +0000</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -13259,40 +12854,40 @@
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:12:12 +0000</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -13310,39 +12905,39 @@
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:08:19 +0000</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -13360,39 +12955,39 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:17:27 +0000</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -13431,39 +13026,39 @@
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:16:32 +0000</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -13481,39 +13076,39 @@
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:16:13 +0000</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F253" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, xiao jianming:
@@ -13531,40 +13126,40 @@
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:15:21 +0000</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F254" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr"/>
-      <c r="H254" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -13582,39 +13177,39 @@
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B255" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:13:24 +0000</t>
         </is>
       </c>
-      <c r="E255" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F255" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>Documents de sécurité des produits requis pour les garder actifs</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr"/>
-      <c r="H255" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour xiao jianming,
@@ -13632,39 +13227,39 @@
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 13:34:40 +0000</t>
         </is>
       </c>
-      <c r="E256" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F256" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr"/>
-      <c r="H256" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -13679,39 +13274,39 @@
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 17:10:30 +0000</t>
         </is>
       </c>
-      <c r="E257" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F257" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr"/>
-      <c r="H257" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -13729,40 +13324,40 @@
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 04:55:50 +0000</t>
         </is>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F258" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Hemos actualizado los requisitos del distintivo de Prime para Prime
  Day</t>
         </is>
       </c>
-      <c r="G258" s="2" t="inlineStr"/>
-      <c r="H258" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>96
  Para ayudarte a mantener el distintivo de Prime durante Prime Day, hemos actualizado nuestros requisitos del distintivo en España.
@@ -13783,39 +13378,39 @@
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D259" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:49:02 +0000</t>
         </is>
       </c>
-      <c r="E259" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F259" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr"/>
-      <c r="H259" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Actualización de estado de mercancías peligrosas
@@ -13837,39 +13432,39 @@
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D260" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:44:43 +0000</t>
         </is>
       </c>
-      <c r="E260" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F260" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr"/>
-      <c r="H260" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>96
  Status materiałów niebezpiecznych (hazmat)
@@ -13889,39 +13484,39 @@
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D261" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:35:25 +0000</t>
         </is>
       </c>
-      <c r="E261" s="2" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F261" s="2" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>Mise à jour du statut des matières dangereuses (Hazmat)</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr"/>
-      <c r="H261" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>96
  Mise à jour du statut des matières dangereuses (Hazmat)
@@ -13933,39 +13528,39 @@
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C262" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D262" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:03:25 +0000</t>
         </is>
       </c>
-      <c r="E262" s="2" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F262" s="2" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G262" s="2" t="inlineStr"/>
-      <c r="H262" s="2" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiornamento dello stato delle merci pericolose
@@ -13977,39 +13572,39 @@
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D263" s="2" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:03:17 +0000</t>
         </is>
       </c>
-      <c r="E263" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F263" s="2" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>Update van status gevaarlijke goederen</t>
         </is>
       </c>
-      <c r="G263" s="2" t="inlineStr"/>
-      <c r="H263" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>96
  Update van status gevaarlijke goederen
@@ -14031,39 +13626,39 @@
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 11:41:38 +0000</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>"Pereira, Sheryl" &lt;persher@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F264" s="2" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>Amazon India your next growth market</t>
         </is>
       </c>
-      <c r="G264" s="2" t="inlineStr"/>
-      <c r="H264" s="2" t="inlineStr">
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>Hi Team,
 Sheryl this side from Amazon India Out of Country team, we work with high-potential global brands to successfully launch and scale their presence in India. Given the current selection gaps and growing customer demand, I believe Amazon.in could be a great opportunity for Roaxkois
@@ -14077,39 +13672,39 @@
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B265" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D265" s="2" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 08:25:43 +0000</t>
         </is>
       </c>
-      <c r="E265" s="2" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F265" s="2" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G265" s="2" t="inlineStr"/>
-      <c r="H265" s="2" t="inlineStr">
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -14137,39 +13732,39 @@
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D266" s="2" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:16:28 +0000</t>
         </is>
       </c>
-      <c r="E266" s="2" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F266" s="2" t="inlineStr">
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>27 lipca rozpocznie się ulepszanie tytułów stron produktów</t>
         </is>
       </c>
-      <c r="G266" s="2" t="inlineStr"/>
-      <c r="H266" s="2" t="inlineStr">
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr">
         <is>
           <t>96
  Tytuły we wszystkich kategoriach (z wyjątkiem kategorii „Media”) będą musiały zawierać 75 znaków lub mniej, łącznie ze spacjami. Nowa funkcja „Najważniejsze informacje” zapewnia dodatkowe 125 znaków, umożliwiając udostępnianie materiałów.
@@ -14180,40 +13775,40 @@
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D267" s="2" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:08:24 +0000</t>
         </is>
       </c>
-      <c r="E267" s="2" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F267" s="2" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti per migliorare i titoli dei prodotti a partire dal 27
  luglio</t>
         </is>
       </c>
-      <c r="G267" s="2" t="inlineStr"/>
-      <c r="H267" s="2" t="inlineStr">
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <t>96
  I titoli in tutte le categorie eccetto i prodotti multimediali dovranno contenere un massimo di 75 caratteri, spazi inclusi. Nelle caratteristiche principali dei prodotti, saranno ora disponibili altri 125 caratteri per descrivere i materiali.
@@ -14224,39 +13819,39 @@
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D268" s="2" t="inlineStr">
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:05:34 +0000</t>
         </is>
       </c>
-      <c r="E268" s="2" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F268" s="2" t="inlineStr">
+      <c r="F260" s="2" t="inlineStr">
         <is>
           <t>Updates om je producttitels te verbeteren beginnen op 27 juli</t>
         </is>
       </c>
-      <c r="G268" s="2" t="inlineStr"/>
-      <c r="H268" s="2" t="inlineStr">
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="inlineStr">
         <is>
           <t>96
  Titels in alle categorieën, behalve in de categorie ‘media’ mogen maximaal 75 tekens lang zijn, inclusief spaties. Met de nieuwe functie Itemhoogtepunten kun je nu 125 extra tekens gebruiken om materiaal te delen.
@@ -14268,39 +13863,39 @@
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D269" s="2" t="inlineStr">
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:05:16 +0000</t>
         </is>
       </c>
-      <c r="E269" s="2" t="inlineStr">
+      <c r="E261" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F269" s="2" t="inlineStr">
+      <c r="F261" s="2" t="inlineStr">
         <is>
           <t>Las actualizaciones para mejorar los títulos de los productos entrarán en vigor el 27 de julio</t>
         </is>
       </c>
-      <c r="G269" s="2" t="inlineStr"/>
-      <c r="H269" s="2" t="inlineStr">
+      <c r="G261" s="2" t="inlineStr"/>
+      <c r="H261" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Los títulos de todas las categorías, excepto multimedia, tendrán que tener 75 caracteres o menos, contando espacios. La nueva herramienta de aspectos destacados del producto ahora ofrece 125 caracteres más para compartir materiales.
@@ -14311,39 +13906,39 @@
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B270" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C270" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D270" s="2" t="inlineStr">
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 19:10:59 +0000</t>
         </is>
       </c>
-      <c r="E270" s="2" t="inlineStr">
+      <c r="E262" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F270" s="2" t="inlineStr">
+      <c r="F262" s="2" t="inlineStr">
         <is>
           <t>Nueva restricción de la UE sobre la puesta de inventario de productos textiles y calzado a disposición de Amazon</t>
         </is>
       </c>
-      <c r="G270" s="2" t="inlineStr"/>
-      <c r="H270" s="2" t="inlineStr">
+      <c r="G262" s="2" t="inlineStr"/>
+      <c r="H262" s="2" t="inlineStr">
         <is>
           <t>96
  A más tardar el 19 de julio, actualiza la configuración de retiradas de prendas de vestir y calzado en los centros logísticos de la UE
@@ -14356,40 +13951,40 @@
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="2" t="inlineStr">
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D271" s="2" t="inlineStr">
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 19:03:48 +0000</t>
         </is>
       </c>
-      <c r="E271" s="2" t="inlineStr">
+      <c r="E263" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F271" s="2" t="inlineStr">
+      <c r="F263" s="2" t="inlineStr">
         <is>
           <t>Nuove limitazioni dell'Unione europea sul reimpiego di prodotti
  tessili e calzature</t>
         </is>
       </c>
-      <c r="G271" s="2" t="inlineStr"/>
-      <c r="H271" s="2" t="inlineStr">
+      <c r="G263" s="2" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiorna le impostazioni di rimozione per capi di abbigliamento, accessori e calzature nei centri logistici dell'Unione europea entro il 19 luglio
@@ -14402,39 +13997,39 @@
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B272" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D272" s="2" t="inlineStr">
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 18:26:32 +0000</t>
         </is>
       </c>
-      <c r="E272" s="2" t="inlineStr">
+      <c r="E264" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F272" s="2" t="inlineStr">
+      <c r="F264" s="2" t="inlineStr">
         <is>
           <t>Nowe ograniczenia UE dotyczące usuwania tekstyliów i obuwia</t>
         </is>
       </c>
-      <c r="G272" s="2" t="inlineStr"/>
-      <c r="H272" s="2" t="inlineStr">
+      <c r="G264" s="2" t="inlineStr"/>
+      <c r="H264" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Do 19 lipca zmień ustawienia wycofywania zapasów odzieży i obuwia magazynowanych w centrach logistycznych w UE
@@ -14448,39 +14043,39 @@
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="2" t="inlineStr">
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B273" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D273" s="2" t="inlineStr">
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 18:08:34 +0000</t>
         </is>
       </c>
-      <c r="E273" s="2" t="inlineStr">
+      <c r="E265" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F273" s="2" t="inlineStr">
+      <c r="F265" s="2" t="inlineStr">
         <is>
           <t>Nouvelle restriction de l’UE sur la mise au rebut des textiles et des chaussures</t>
         </is>
       </c>
-      <c r="G273" s="2" t="inlineStr"/>
-      <c r="H273" s="2" t="inlineStr">
+      <c r="G265" s="2" t="inlineStr"/>
+      <c r="H265" s="2" t="inlineStr">
         <is>
           <t>96
  D’ici le 19 juillet, mettez à jour vos paramètres de demande de prélèvement pour les vêtements, les accessoires vestimentaires et les chaussures dans les centres de distribution de l’UE
@@ -14493,39 +14088,39 @@
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D274" s="2" t="inlineStr">
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:46:44 +0000</t>
         </is>
       </c>
-      <c r="E274" s="2" t="inlineStr">
+      <c r="E266" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F274" s="2" t="inlineStr">
+      <c r="F266" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr"/>
-      <c r="H274" s="2" t="inlineStr">
+      <c r="G266" s="2" t="inlineStr"/>
+      <c r="H266" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14549,39 +14144,39 @@
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C275" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D275" s="2" t="inlineStr">
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:45:39 +0000</t>
         </is>
       </c>
-      <c r="E275" s="2" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F275" s="2" t="inlineStr">
+      <c r="F267" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G275" s="2" t="inlineStr"/>
-      <c r="H275" s="2" t="inlineStr">
+      <c r="G267" s="2" t="inlineStr"/>
+      <c r="H267" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14605,39 +14200,39 @@
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B276" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 03:25:54 +0000</t>
         </is>
       </c>
-      <c r="E276" s="2" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F276" s="2" t="inlineStr">
+      <c r="F268" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-09</t>
         </is>
       </c>
-      <c r="G276" s="2" t="inlineStr"/>
-      <c r="H276" s="2" t="inlineStr">
+      <c r="G268" s="2" t="inlineStr"/>
+      <c r="H268" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14659,39 +14254,39 @@
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" s="2" t="inlineStr">
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B277" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C277" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D277" s="2" t="inlineStr">
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 04:59:29 +0000</t>
         </is>
       </c>
-      <c r="E277" s="2" t="inlineStr">
+      <c r="E269" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F277" s="2" t="inlineStr">
+      <c r="F269" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G277" s="2" t="inlineStr"/>
-      <c r="H277" s="2" t="inlineStr">
+      <c r="G269" s="2" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14715,39 +14310,39 @@
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B278" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C278" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D278" s="2" t="inlineStr">
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 03:24:34 +0000</t>
         </is>
       </c>
-      <c r="E278" s="2" t="inlineStr">
+      <c r="E270" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F278" s="2" t="inlineStr">
+      <c r="F270" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-02</t>
         </is>
       </c>
-      <c r="G278" s="2" t="inlineStr"/>
-      <c r="H278" s="2" t="inlineStr">
+      <c r="G270" s="2" t="inlineStr"/>
+      <c r="H270" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14769,39 +14364,39 @@
         </is>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" s="2" t="inlineStr">
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B279" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C279" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D279" s="2" t="inlineStr">
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 04:57:38 +0000</t>
         </is>
       </c>
-      <c r="E279" s="2" t="inlineStr">
+      <c r="E271" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F279" s="2" t="inlineStr">
+      <c r="F271" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-25</t>
         </is>
       </c>
-      <c r="G279" s="2" t="inlineStr"/>
-      <c r="H279" s="2" t="inlineStr">
+      <c r="G271" s="2" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14823,39 +14418,39 @@
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" s="2" t="inlineStr">
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B280" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D280" s="2" t="inlineStr">
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 04:53:34 +0000</t>
         </is>
       </c>
-      <c r="E280" s="2" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F280" s="2" t="inlineStr">
+      <c r="F272" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-25</t>
         </is>
       </c>
-      <c r="G280" s="2" t="inlineStr"/>
-      <c r="H280" s="2" t="inlineStr">
+      <c r="G272" s="2" t="inlineStr"/>
+      <c r="H272" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14879,39 +14474,39 @@
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" s="2" t="inlineStr">
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B281" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C281" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D281" s="2" t="inlineStr">
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 00:16:50 +0000</t>
         </is>
       </c>
-      <c r="E281" s="2" t="inlineStr">
+      <c r="E273" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F281" s="2" t="inlineStr">
+      <c r="F273" s="2" t="inlineStr">
         <is>
           <t>View your US Q3-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G281" s="2" t="inlineStr"/>
-      <c r="H281" s="2" t="inlineStr">
+      <c r="G273" s="2" t="inlineStr"/>
+      <c r="H273" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q3-2026
@@ -14941,39 +14536,39 @@
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" s="2" t="inlineStr">
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B282" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D282" s="2" t="inlineStr">
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 12:14:25 +0000</t>
         </is>
       </c>
-      <c r="E282" s="2" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F282" s="2" t="inlineStr">
+      <c r="F274" s="2" t="inlineStr">
         <is>
           <t>Connect with an Amazon expert at Seller Café—Save $100 with early-bird pricing</t>
         </is>
       </c>
-      <c r="G282" s="2" t="inlineStr"/>
-      <c r="H282" s="2" t="inlineStr">
+      <c r="G274" s="2" t="inlineStr"/>
+      <c r="H274" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z46y96/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/4uHYwMZ-ld-EM/7z46y99/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
@@ -14989,39 +14584,39 @@
         </is>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" s="2" t="inlineStr">
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B283" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C283" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D283" s="2" t="inlineStr">
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 03:04:08 +0000</t>
         </is>
       </c>
-      <c r="E283" s="2" t="inlineStr">
+      <c r="E275" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F283" s="2" t="inlineStr">
+      <c r="F275" s="2" t="inlineStr">
         <is>
           <t>Action Required: Transparency Barcode Required for Your Products</t>
         </is>
       </c>
-      <c r="G283" s="2" t="inlineStr"/>
-      <c r="H283" s="2" t="inlineStr">
+      <c r="G275" s="2" t="inlineStr"/>
+      <c r="H275" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello from Amazon Seller Services,
@@ -15037,39 +14632,39 @@
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" s="2" t="inlineStr">
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B284" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C284" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D284" s="2" t="inlineStr">
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 08:49:28 +0000</t>
         </is>
       </c>
-      <c r="E284" s="2" t="inlineStr">
+      <c r="E276" s="2" t="inlineStr">
         <is>
           <t>"Gao, Mark" &lt;gaomark@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F284" s="2" t="inlineStr">
+      <c r="F276" s="2" t="inlineStr">
         <is>
           <t>亚马逊广告限时激励活动 - Weihai EU</t>
         </is>
       </c>
-      <c r="G284" s="2" t="inlineStr"/>
-      <c r="H284" s="2" t="inlineStr">
+      <c r="G276" s="2" t="inlineStr"/>
+      <c r="H276" s="2" t="inlineStr">
         <is>
           <t>Amazon has replaced the attachment in this email with download link.
 Important: This link may contain content that is confidential. Please exercise appropriate caution when sharing.
@@ -15097,39 +14692,39 @@
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" s="2" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B285" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C285" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D285" s="2" t="inlineStr">
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:43:31 +0000</t>
         </is>
       </c>
-      <c r="E285" s="2" t="inlineStr">
+      <c r="E277" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F285" s="2" t="inlineStr">
+      <c r="F277" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G285" s="2" t="inlineStr"/>
-      <c r="H285" s="2" t="inlineStr">
+      <c r="G277" s="2" t="inlineStr"/>
+      <c r="H277" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -15151,39 +14746,39 @@
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" s="2" t="inlineStr">
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B286" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C286" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D286" s="2" t="inlineStr">
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:43:28 +0000</t>
         </is>
       </c>
-      <c r="E286" s="2" t="inlineStr">
+      <c r="E278" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F286" s="2" t="inlineStr">
+      <c r="F278" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G286" s="2" t="inlineStr"/>
-      <c r="H286" s="2" t="inlineStr">
+      <c r="G278" s="2" t="inlineStr"/>
+      <c r="H278" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -15205,39 +14800,39 @@
         </is>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" s="2" t="inlineStr">
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B287" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C287" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D287" s="2" t="inlineStr">
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 11:03:54 +0000</t>
         </is>
       </c>
-      <c r="E287" s="2" t="inlineStr">
+      <c r="E279" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F287" s="2" t="inlineStr">
+      <c r="F279" s="2" t="inlineStr">
         <is>
           <t>You have until July 17 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G287" s="2" t="inlineStr"/>
-      <c r="H287" s="2" t="inlineStr">
+      <c r="G279" s="2" t="inlineStr"/>
+      <c r="H279" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
@@ -15246,39 +14841,39 @@
         </is>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" s="2" t="inlineStr">
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B288" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C288" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D288" s="2" t="inlineStr">
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:33:42 +0000</t>
         </is>
       </c>
-      <c r="E288" s="2" t="inlineStr">
+      <c r="E280" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F288" s="2" t="inlineStr">
+      <c r="F280" s="2" t="inlineStr">
         <is>
           <t>Updates to improve your product titles begin on July 27</t>
         </is>
       </c>
-      <c r="G288" s="2" t="inlineStr"/>
-      <c r="H288" s="2" t="inlineStr">
+      <c r="G280" s="2" t="inlineStr"/>
+      <c r="H280" s="2" t="inlineStr">
         <is>
           <t>96
  Titles in all categories except for media will need to be 75 characters or less including spaces. A new Item Highlights feature now provides an additional 125 characters for sharing materials.
@@ -15290,39 +14885,39 @@
         </is>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" s="2" t="inlineStr">
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B289" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C289" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D289" s="2" t="inlineStr">
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:07:52 +0000</t>
         </is>
       </c>
-      <c r="E289" s="2" t="inlineStr">
+      <c r="E281" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F289" s="2" t="inlineStr">
+      <c r="F281" s="2" t="inlineStr">
         <is>
           <t>Updates to improve your product titles begin on July 27</t>
         </is>
       </c>
-      <c r="G289" s="2" t="inlineStr"/>
-      <c r="H289" s="2" t="inlineStr">
+      <c r="G281" s="2" t="inlineStr"/>
+      <c r="H281" s="2" t="inlineStr">
         <is>
           <t>96
  Titles in all categories except media will need to be 75 characters or less, including spaces. A new Item Highlights feature now provides an additional 125 characters for sharing materials.
@@ -15334,39 +14929,39 @@
         </is>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" s="2" t="inlineStr">
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B290" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C290" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D290" s="2" t="inlineStr">
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:04:50 +0000</t>
         </is>
       </c>
-      <c r="E290" s="2" t="inlineStr">
+      <c r="E282" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F290" s="2" t="inlineStr">
+      <c r="F282" s="2" t="inlineStr">
         <is>
           <t>Updates to improve your product titles begin on July 27</t>
         </is>
       </c>
-      <c r="G290" s="2" t="inlineStr"/>
-      <c r="H290" s="2" t="inlineStr">
+      <c r="G282" s="2" t="inlineStr"/>
+      <c r="H282" s="2" t="inlineStr">
         <is>
           <t>96
  Titles in all categories except for media will need to be 75 characters or less including spaces. A new Item Highlights feature now provides an additional 125 characters for sharing materials.
@@ -15378,39 +14973,39 @@
         </is>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" s="2" t="inlineStr">
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B291" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C291" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D291" s="2" t="inlineStr">
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 19:18:13 +0000</t>
         </is>
       </c>
-      <c r="E291" s="2" t="inlineStr">
+      <c r="E283" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F291" s="2" t="inlineStr">
+      <c r="F283" s="2" t="inlineStr">
         <is>
           <t>Updates to improve your product titles begin on July 27</t>
         </is>
       </c>
-      <c r="G291" s="2" t="inlineStr"/>
-      <c r="H291" s="2" t="inlineStr">
+      <c r="G283" s="2" t="inlineStr"/>
+      <c r="H283" s="2" t="inlineStr">
         <is>
           <t>96
  Titles in all categories except for media will need to be 75 characters or less, including spaces. A new item highlights feature now provides an additional 125 characters for sharing materials.
@@ -15422,109 +15017,6 @@
         </is>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B292" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C292" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D292" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 14:50:02 +0000</t>
-        </is>
-      </c>
-      <c r="E292" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F292" s="2" t="inlineStr">
-        <is>
-          <t>Earn up to €240 per shipment with C2S2 PCP Pallets</t>
-        </is>
-      </c>
-      <c r="G292" s="2" t="inlineStr"/>
-      <c r="H292" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z3yyjt/6708104655/h/1UCuxAj2NkD65NTovD-vcIwWERBh1hVRp_O_epQxzho)
-C2S2 PCP Pallet Spring Promotion: Ship More, Save More
-Dear Selling Partner,
-Whether you're already shipping pallets, using our SPD solution, or exploring cross-border expansion for the first time, now is the time to act. Our Customs Clearance and Shipping Service (C2S2) PCP Pallet Spring Promotion ends June 30, and every qualifying shipment earns you up to €240 in transportation fee reimbursements.
-🚀 Prime Days are coming: Start inbounding now to be ready for Prime Day. Ship during the promotion and your inventory arrives at European FCs in time for peak demand, while you earn reimbursements on every shipment.
-[Create your next pallet shipment now](https://go.amazonsellerservices.com/e/229492/cb-95cc-4663-98dd-0d07a85a11a0/7z3yyjx/6708104655/h/1UCuxAj2NkD65NTovD-vcIwWERBh1hVRp_O_epQxzho)
-Reimbursement Tiers:
-Pallets per Shipment
-Your Savings
-1-5 pallets
-€60 reimbursement per shipment
-6-10 pallets
-€180 reimbursement per shipment
-11-15 pallets
-€240 reimbursement per shipment
-- Automatic tracking: No claims process - we track your shipments automatically
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B293" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C293" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D293" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 11:06:34 +0000</t>
-        </is>
-      </c>
-      <c r="E293" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon stranded inventory &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F293" s="2" t="inlineStr">
-        <is>
-          <t>Review stranded inventory scheduled for automatic removal</t>
-        </is>
-      </c>
-      <c r="G293" s="2" t="inlineStr"/>
-      <c r="H293" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-Fix stranded inventory
- Take action to prevent unnecessary removal of your stranded inventory
- Review stranded inventory scheduled for automatic removal
- You are receiving this message because you have stranded inventory in an Amazon fulfillment center that is scheduled for automatic removal. For a full view of stranded units scheduled for automatic removal, visit the stranded inventory dashboard and sort by Auto removal date.
- Review stranded inventory
- Why is this happening?
- Inventory can be scheduled for automatic removal for a variety of reasons. In this case, the reason is that the inventory is stranded. Stranded inventory is inventory without a buyable offer and requires you to either reactivate the listing or remove the inventory.
- What happens if I don't take action?
- Your stranded inventory will be returned or disposed of based on the settings you selected on "Fix stranded inventory". To customize your settings, go to Fix stranded inventory and select Edit automatic action settings.
- If you need more time to appeal or fix a stranded inventory issue, go to Fix stranded inventory and select Delay auto removal for 30 days from the drop-down menu for each listing.
- Report </t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
